--- a/data/trans_camb/POLIPATOLOGIA_Lim_2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_2-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 4,9</t>
+          <t>-4,43; 5,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 5,47</t>
+          <t>-3,04; 5,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 6,91</t>
+          <t>-4,1; 7,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 16,68</t>
+          <t>5,91; 16,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 4,54</t>
+          <t>-2,6; 4,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 9,26</t>
+          <t>2,55; 9,11</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,37; 50,28</t>
+          <t>-32,93; 52,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 57,49</t>
+          <t>-22,09; 58,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,48; 73,5</t>
+          <t>-27,4; 81,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39,41; 195,59</t>
+          <t>36,29; 180,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 45,25</t>
+          <t>-18,73; 43,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,92; 91,98</t>
+          <t>18,07; 88,83</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 3,57</t>
+          <t>-6,09; 3,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 6,73</t>
+          <t>-2,53; 6,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 1,67</t>
+          <t>-10,81; 1,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 13,62</t>
+          <t>2,09; 13,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 0,92</t>
+          <t>-6,63; 0,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 8,84</t>
+          <t>0,68; 8,24</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,42; 34,2</t>
+          <t>-39,38; 27,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 63,23</t>
+          <t>-15,71; 64,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,14; 10,78</t>
+          <t>-47,47; 6,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,4; 90,9</t>
+          <t>8,55; 84,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,69; 6,41</t>
+          <t>-37,37; 6,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 65,28</t>
+          <t>3,81; 59,02</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,86; -1,73</t>
+          <t>-10,96; -1,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,49; -1,48</t>
+          <t>-20,32; -1,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 13,06</t>
+          <t>-6,13; 13,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,49; 19,31</t>
+          <t>1,79; 18,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 0,37</t>
+          <t>-8,62; 0,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 1,88</t>
+          <t>-17,15; 1,58</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-43,52; -8,25</t>
+          <t>-44,53; -6,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-80,64; -6,83</t>
+          <t>-79,92; -6,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 52,1</t>
+          <t>-19,77; 53,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,83; 79,39</t>
+          <t>5,21; 73,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,68; 1,51</t>
+          <t>-32,81; 0,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,57; 7,8</t>
+          <t>-64,89; 6,74</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,51; -0,18</t>
+          <t>-6,32; 0,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 6,16</t>
+          <t>-0,89; 5,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 3,18</t>
+          <t>-5,51; 2,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 9,35</t>
+          <t>-9,14; 9,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 0,25</t>
+          <t>-4,89; 0,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 5,66</t>
+          <t>-5,29; 5,87</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,38; -0,98</t>
+          <t>-29,86; 2,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 33,77</t>
+          <t>-4,05; 32,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,12; 17,25</t>
+          <t>-23,89; 15,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,63; 46,82</t>
+          <t>-40,61; 45,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 1,53</t>
+          <t>-22,73; 1,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 29,15</t>
+          <t>-24,31; 29,87</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 6,66</t>
+          <t>-2,91; 6,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 10,29</t>
+          <t>0,24; 10,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 1,72</t>
+          <t>-7,7; 2,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 5,46</t>
+          <t>-10,83; 5,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 2,09</t>
+          <t>-5,58; 1,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 6,49</t>
+          <t>-4,02; 6,21</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 41,22</t>
+          <t>-14,24; 38,33</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 65,21</t>
+          <t>0,94; 65,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,25; 5,02</t>
+          <t>-19,76; 7,1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 15,35</t>
+          <t>-27,87; 16,13</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 7,55</t>
+          <t>-17,73; 6,08</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 23,48</t>
+          <t>-12,98; 22,08</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 2,63</t>
+          <t>-3,94; 2,47</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,61; 14,78</t>
+          <t>1,67; 13,71</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-10,89; -2,38</t>
+          <t>-10,75; -2,68</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 2,96</t>
+          <t>-5,57; 3,04</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,19; -2,32</t>
+          <t>-9,22; -1,85</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 2,7</t>
+          <t>-5,17; 2,66</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-75,3; 234,37</t>
+          <t>-74,89; 214,66</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5,06; 759,2</t>
+          <t>-0,23; 836,02</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-27,46; -6,67</t>
+          <t>-26,77; -7,34</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 8,19</t>
+          <t>-14,06; 8,38</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-28,33; -7,84</t>
+          <t>-28,21; -6,45</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 9,15</t>
+          <t>-16,19; 9,03</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,81; -0,2</t>
+          <t>-3,75; -0,11</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 2,51</t>
+          <t>-3,46; 2,53</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,66; -1,36</t>
+          <t>-5,72; -1,38</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 3,78</t>
+          <t>-4,76; 3,83</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,25; -1,3</t>
+          <t>-4,28; -1,37</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 2,77</t>
+          <t>-2,58; 2,75</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-21,1; -1,17</t>
+          <t>-21,08; -0,66</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-21,31; 15,52</t>
+          <t>-20,27; 15,45</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-18,79; -4,8</t>
+          <t>-19,2; -4,88</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 13,31</t>
+          <t>-15,72; 13,49</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-17,74; -5,83</t>
+          <t>-18,04; -6,14</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 12,12</t>
+          <t>-10,94; 12,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_Lim_2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_2-Clase-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,42</t>
+          <t>11,51</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,97</t>
+          <t>6,17</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 5,0</t>
+          <t>-4,44; 5,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 5,55</t>
+          <t>-2,81; 5,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 7,21</t>
+          <t>-3,59; 7,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,91; 16,02</t>
+          <t>6,18; 16,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 4,58</t>
+          <t>-2,44; 4,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 9,11</t>
+          <t>3,06; 9,43</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>51,55%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,93; 52,84</t>
+          <t>-31,5; 50,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 58,77</t>
+          <t>-20,33; 56,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,4; 81,23</t>
+          <t>-26,51; 76,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,29; 180,49</t>
+          <t>37,64; 185,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 43,5</t>
+          <t>-18,56; 43,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,07; 88,83</t>
+          <t>20,76; 94,81</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,82</t>
+          <t>8,54</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>4,87</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 3,06</t>
+          <t>-6,45; 3,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 6,68</t>
+          <t>-3,65; 5,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 1,03</t>
+          <t>-10,01; 1,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 13,13</t>
+          <t>1,78; 13,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 0,99</t>
+          <t>-7,01; 0,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 8,24</t>
+          <t>0,87; 8,77</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,56%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,38; 27,05</t>
+          <t>-40,44; 34,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 64,3</t>
+          <t>-21,98; 56,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,47; 6,42</t>
+          <t>-45,93; 10,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,55; 84,19</t>
+          <t>7,97; 90,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,37; 6,87</t>
+          <t>-37,69; 6,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 59,02</t>
+          <t>4,31; 63,12</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-10,35</t>
+          <t>-4,19</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,64</t>
+          <t>9,92</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-6,75</t>
+          <t>-0,23</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,96; -1,37</t>
+          <t>-11,0; -1,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,32; -1,5</t>
+          <t>-9,33; 0,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 13,27</t>
+          <t>-6,52; 12,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 18,36</t>
+          <t>1,57; 18,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 0,04</t>
+          <t>-8,89; 0,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 1,58</t>
+          <t>-4,32; 4,37</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-46,27%</t>
+          <t>-18,75%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-27,84%</t>
+          <t>-0,94%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,53; -6,72</t>
+          <t>-44,07; -7,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,92; -6,77</t>
+          <t>-36,69; 3,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,77; 53,25</t>
+          <t>-19,55; 49,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,21; 73,61</t>
+          <t>4,44; 73,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,81; 0,29</t>
+          <t>-34,06; 0,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,89; 6,74</t>
+          <t>-16,41; 19,95</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,54</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>8,07</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>4,87</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 0,45</t>
+          <t>-6,44; 0,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 5,9</t>
+          <t>-0,89; 6,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 2,87</t>
+          <t>-5,25; 3,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 9,21</t>
+          <t>3,72; 11,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 0,29</t>
+          <t>-4,93; 0,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 5,87</t>
+          <t>2,34; 7,38</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-29,86; 2,19</t>
+          <t>-30,39; 0,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 32,96</t>
+          <t>-4,31; 34,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 15,84</t>
+          <t>-22,93; 18,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,61; 45,96</t>
+          <t>16,36; 64,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,73; 1,52</t>
+          <t>-23,35; 3,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-24,31; 29,87</t>
+          <t>10,38; 39,01</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>2,95</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>2,8</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 6,14</t>
+          <t>-2,84; 6,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,24; 10,78</t>
+          <t>-1,73; 7,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 2,39</t>
+          <t>-8,39; 1,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 5,73</t>
+          <t>-1,59; 7,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 1,71</t>
+          <t>-5,53; 1,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 6,21</t>
+          <t>-0,61; 6,15</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-1,45%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -1331,39 +1331,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 38,33</t>
+          <t>-14,27; 38,1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,94; 65,91</t>
+          <t>-8,78; 47,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 7,1</t>
+          <t>-20,88; 5,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-27,87; 16,13</t>
+          <t>-3,9; 21,28</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 6,08</t>
+          <t>-17,29; 5,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 22,08</t>
+          <t>-1,91; 22,56</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6,71</t>
+          <t>6,74</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-2,06</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,09</t>
+          <t>-1,01</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 2,47</t>
+          <t>-3,92; 2,38</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,67; 13,71</t>
+          <t>1,76; 14,63</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-10,75; -2,68</t>
+          <t>-10,72; -2,49</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 3,04</t>
+          <t>-6,43; 2,47</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,22; -1,85</t>
+          <t>-8,89; -1,88</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 2,66</t>
+          <t>-4,78; 2,86</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>218,99%</t>
+          <t>220,15%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-3,85%</t>
+          <t>-5,45%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-3,53%</t>
+          <t>-3,25%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-74,89; 214,66</t>
+          <t>-74,07; 186,31</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 836,02</t>
+          <t>17,47; 1062,16</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-26,77; -7,34</t>
+          <t>-26,54; -6,83</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 8,38</t>
+          <t>-16,12; 6,98</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-28,21; -6,45</t>
+          <t>-27,41; -6,2</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 9,03</t>
+          <t>-14,67; 9,94</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>3,39</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>2,39</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,75; -0,11</t>
+          <t>-3,86; -0,21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 2,53</t>
+          <t>-0,86; 3,08</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,72; -1,38</t>
+          <t>-5,88; -1,27</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 3,83</t>
+          <t>1,3; 5,46</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,28; -1,37</t>
+          <t>-4,24; -1,17</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,75</t>
+          <t>1,04; 3,87</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-21,08; -0,66</t>
+          <t>-21,49; -1,51</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-20,27; 15,45</t>
+          <t>-4,9; 18,9</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,2; -4,88</t>
+          <t>-19,41; -4,66</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 13,49</t>
+          <t>4,32; 19,84</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-18,04; -6,14</t>
+          <t>-17,6; -5,22</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 12,07</t>
+          <t>4,48; 17,29</t>
         </is>
       </c>
     </row>
